--- a/csharp/Wjybxx.BigCatEditor.Tests/res/test.xlsx
+++ b/csharp/Wjybxx.BigCatEditor.Tests/res/test.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="76">
   <si>
     <t>普通表模板</t>
   </si>
@@ -39,10 +39,10 @@
     <t>已废弃的古老的技能配置方式</t>
   </si>
   <si>
-    <t>cs</t>
-  </si>
-  <si>
-    <t>c</t>
+    <t>C/S</t>
+  </si>
+  <si>
+    <t>C</t>
   </si>
   <si>
     <t>int32</t>
@@ -99,59 +99,37 @@
     <t>参数表模板</t>
   </si>
   <si>
-    <t>args</t>
+    <t>options</t>
+  </si>
+  <si>
+    <t>type</t>
   </si>
   <si>
     <t>name</t>
   </si>
   <si>
-    <t>type</t>
-  </si>
-  <si>
     <t>value</t>
   </si>
   <si>
-    <t>DEFAULT_HIT_RATE</t>
+    <t>comment</t>
   </si>
   <si>
     <t>float</t>
   </si>
   <si>
+    <t>baseHitRate</t>
+  </si>
+  <si>
     <t>默认命中率</t>
   </si>
   <si>
-    <t>DEFAULT_CRIT_RATE</t>
+    <t>baseCritRate</t>
   </si>
   <si>
     <t>默认暴击值</t>
   </si>
   <si>
     <t>有常量名的数据不可删</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Microsoft YaHei"/>
-        <charset val="134"/>
-      </rPr>
-      <t>cs</t>
-    </r>
-  </si>
-  <si>
-    <t>cs --skip</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Microsoft YaHei"/>
-        <charset val="134"/>
-      </rPr>
-      <t>c</t>
-    </r>
   </si>
   <si>
     <r>
@@ -242,12 +220,6 @@
     <t>试炼武馆</t>
   </si>
   <si>
-    <t>C/S</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="10.5"/>
@@ -259,6 +231,9 @@
     </r>
   </si>
   <si>
+    <t>List&lt;string&gt;</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10.5"/>
@@ -292,6 +267,15 @@
     </r>
   </si>
   <si>
+    <t>jumpList</t>
+  </si>
+  <si>
+    <t>jumpList#1</t>
+  </si>
+  <si>
+    <t>jumpList#2</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10.5"/>
@@ -336,6 +320,15 @@
     </r>
   </si>
   <si>
+    <t>测试List合并</t>
+  </si>
+  <si>
+    <t>跳表1</t>
+  </si>
+  <si>
+    <t>跳表2</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10.5"/>
@@ -347,6 +340,12 @@
     </r>
   </si>
   <si>
+    <t>linker_101</t>
+  </si>
+  <si>
+    <t>linker_102</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10.5"/>
@@ -356,6 +355,12 @@
       </rPr>
       <t>2号物品</t>
     </r>
+  </si>
+  <si>
+    <t>linker_201</t>
+  </si>
+  <si>
+    <t>linker_202</t>
   </si>
   <si>
     <t>double</t>
@@ -386,7 +391,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -398,19 +403,6 @@
       <sz val="10.5"/>
       <color rgb="FF000000"/>
       <name val="Microsoft YaHei"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Helvetica"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Helvetica"/>
       <charset val="134"/>
     </font>
     <font>
@@ -558,7 +550,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -567,12 +559,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -758,42 +744,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="9">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFA7A7A7"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFA7A7A7"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFA7A7A7"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFA7A7A7"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFDDDDDD"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFDDDDDD"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFDDDDDD"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFDDDDDD"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -914,151 +870,163 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1411,115 +1379,183 @@
   <dimension ref="A1:E16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="12.75" customWidth="1"/>
-    <col min="2" max="2" width="12.3796296296296" customWidth="1"/>
-    <col min="3" max="3" width="15.25" customWidth="1"/>
-    <col min="4" max="4" width="14.8796296296296" customWidth="1"/>
-    <col min="5" max="5" width="15.8796296296296" customWidth="1"/>
+    <col min="1" max="1" width="12.75" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.3796296296296" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.25" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14.8796296296296" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.8796296296296" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
+    <row r="1" ht="15.6" spans="1:5">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" ht="15.15"/>
-    <row r="11" ht="15.15" spans="1:4">
-      <c r="A11" s="3" t="s">
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+    </row>
+    <row r="2" ht="15.6" spans="1:5">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+    </row>
+    <row r="3" ht="15.6" spans="1:5">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4" ht="15.6" spans="1:5">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5" ht="15.6" spans="1:5">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" ht="15.6" spans="1:5">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" ht="15.6" spans="1:5">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="6"/>
+    </row>
+    <row r="8" ht="15.6" spans="1:5">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" ht="15.6" spans="1:5">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="8"/>
+    </row>
+    <row r="10" ht="15.6" spans="1:5">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11" ht="15.6" spans="1:5">
+      <c r="A11" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="12" ht="15.15" spans="1:4">
-      <c r="A12" s="4" t="s">
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12" ht="15.6" spans="1:5">
+      <c r="A12" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="13" ht="15.15" spans="1:5">
-      <c r="A13" s="4" t="s">
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13" ht="15.6" spans="1:5">
+      <c r="A13" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="14" ht="15.15" spans="1:5">
-      <c r="A14" s="4" t="s">
+    <row r="14" ht="15.6" spans="1:5">
+      <c r="A14" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="15" ht="15.15" spans="1:5">
-      <c r="A15" s="4">
+    <row r="15" ht="15.6" spans="1:5">
+      <c r="A15" s="2">
         <v>10001</v>
       </c>
-      <c r="B15" s="4">
+      <c r="B15" s="2">
         <v>20001</v>
       </c>
-      <c r="C15" s="4" t="b">
+      <c r="C15" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="16" ht="15.15" spans="1:5">
-      <c r="A16" s="4">
+    <row r="16" ht="15.6" spans="1:5">
+      <c r="A16" s="2">
         <v>10002</v>
       </c>
-      <c r="B16" s="4">
+      <c r="B16" s="2">
         <v>20002</v>
       </c>
-      <c r="C16" s="4" t="b">
+      <c r="C16" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="2" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1536,67 +1572,135 @@
   <dimension ref="A1:E13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="11.8888888888889" customWidth="1"/>
-    <col min="2" max="2" width="19.7777777777778" customWidth="1"/>
-    <col min="3" max="4" width="6.66666666666667" customWidth="1"/>
-    <col min="5" max="5" width="11.8888888888889" customWidth="1"/>
-    <col min="6" max="6" width="17.1296296296296" customWidth="1"/>
+    <col min="1" max="1" width="11.8888888888889" style="1" customWidth="1"/>
+    <col min="2" max="2" width="6.66666666666667" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19.7777777777778" style="1" customWidth="1"/>
+    <col min="4" max="4" width="6.66666666666667" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.8888888888889" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" t="s">
+    <row r="1" ht="15.6" spans="1:5">
+      <c r="A1" s="2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+    </row>
+    <row r="2" ht="15.6" spans="1:5">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+    </row>
+    <row r="3" ht="15.6" spans="1:5">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4" ht="15.6" spans="1:5">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5" ht="15.6" spans="1:5">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" ht="15.6" spans="1:5">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" ht="15.6" spans="1:5">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" ht="15.6" spans="1:5">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" ht="15.6" spans="1:5">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" ht="15.6" spans="1:5">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11" ht="15.6" spans="1:5">
+      <c r="A11" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" t="s">
+      <c r="E11" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" ht="15.6" spans="1:5">
+      <c r="A12" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="B12" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D12">
+      <c r="C12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="2">
         <v>0.8</v>
       </c>
-      <c r="E12" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" t="s">
+      <c r="E12" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" ht="15.6" spans="1:5">
+      <c r="A13" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="B13" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D13">
+      <c r="C13" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" s="2">
         <v>0.15</v>
       </c>
-      <c r="E13" t="s">
-        <v>30</v>
+      <c r="E13" s="2" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1609,8 +1713,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A7:E17"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="4"/>
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="10.6666666666667" customWidth="1"/>
     <col min="2" max="2" width="15.5555555555556" customWidth="1"/>
@@ -1619,128 +1723,219 @@
     <col min="5" max="5" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="7" spans="2:2">
-      <c r="B7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" ht="15.15"/>
-    <row r="11" ht="16.35" spans="1:5">
-      <c r="A11" s="1" t="s">
+    <row r="1" ht="15.6" spans="1:6">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+    </row>
+    <row r="2" ht="15.6" spans="1:6">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" ht="15.6" spans="1:6">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+    </row>
+    <row r="4" ht="15.6" spans="1:6">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+    </row>
+    <row r="5" ht="15.6" spans="1:6">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+    </row>
+    <row r="6" ht="15.6" spans="1:6">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+    </row>
+    <row r="7" ht="15.6" spans="1:6">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+    </row>
+    <row r="8" ht="15.6" spans="1:6">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+    </row>
+    <row r="9" ht="15.6" spans="1:6">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" ht="15.6" spans="1:6">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+    </row>
+    <row r="11" ht="15.6" spans="1:6">
+      <c r="A11" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F11" s="2"/>
+    </row>
+    <row r="12" ht="15.6" spans="1:6">
+      <c r="A12" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="B12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D12" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12" s="2"/>
+    </row>
+    <row r="13" ht="15.6" spans="1:6">
+      <c r="A13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13" s="2"/>
+    </row>
+    <row r="14" ht="15.6" spans="1:6">
+      <c r="A14" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F14" s="2"/>
+    </row>
+    <row r="15" ht="15.6" spans="1:6">
+      <c r="A15" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="2">
+        <v>1</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F15" s="2"/>
+    </row>
+    <row r="16" ht="15.6" spans="1:6">
+      <c r="A16" s="2">
+        <v>1002</v>
+      </c>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" s="2">
         <v>2</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12" ht="16.35" spans="1:5">
-      <c r="A12" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" ht="16.35" spans="1:5">
-      <c r="A13" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="14" ht="16.35" spans="1:5">
-      <c r="A14" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="15" ht="16.35" spans="1:5">
-      <c r="A15" s="1">
-        <v>1001</v>
-      </c>
-      <c r="B15" s="1" t="s">
+      <c r="E16" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="F16" s="2"/>
+    </row>
+    <row r="17" ht="15.6" spans="1:6">
+      <c r="A17" s="2">
+        <v>8001</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="1">
-        <v>1</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="16" ht="16.35" spans="1:5">
-      <c r="A16" s="1">
-        <v>1002</v>
-      </c>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1" t="s">
+      <c r="C17" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D16" s="1">
-        <v>2</v>
-      </c>
-      <c r="E16" s="1" t="s">
+      <c r="D17" s="2">
+        <v>20</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="17" ht="16.35" spans="1:5">
-      <c r="A17" s="1">
-        <v>8001</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D17" s="1">
-        <v>20</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>50</v>
-      </c>
+      <c r="F17" s="2"/>
+    </row>
+    <row r="18" ht="15.6" spans="1:6">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1751,91 +1946,148 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A11:D16"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <dimension ref="A11:G16"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="4" width="8.88888888888889" style="4"/>
+    <col min="5" max="5" width="16" style="4" customWidth="1"/>
+    <col min="6" max="6" width="14.4444444444444" style="4" customWidth="1"/>
+    <col min="7" max="7" width="14.1111111111111" style="4" customWidth="1"/>
+    <col min="8" max="16384" width="8.88888888888889" style="4"/>
+  </cols>
   <sheetData>
-    <row r="11" ht="16.35" spans="1:4">
-      <c r="A11" s="1" t="s">
+    <row r="11" ht="15.6" spans="1:7">
+      <c r="A11" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" ht="15.6" spans="1:7">
+      <c r="A12" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" ht="15.6" spans="1:7">
+      <c r="A13" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D11" s="1" t="s">
+      <c r="B13" s="5" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="12" ht="16.35" spans="1:4">
-      <c r="A12" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" s="1" t="s">
+      <c r="C13" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" ht="16.35" spans="1:4">
-      <c r="A13" s="1" t="s">
+      <c r="D13" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="F13" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="G13" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="14" ht="16.35" spans="1:4">
-      <c r="A14" s="1" t="s">
+    </row>
+    <row r="14" ht="15.6" spans="1:7">
+      <c r="A14" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="5" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="15" ht="16.35" spans="1:4">
-      <c r="A15" s="1">
+      <c r="E14" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15" ht="15.6" spans="1:7">
+      <c r="A15" s="5">
         <v>10001</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15" s="5">
         <v>1</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C15" s="5">
         <v>1</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="16" ht="16.35" spans="1:4">
-      <c r="A16" s="1">
+      <c r="D15" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" ht="15.6" spans="1:7">
+      <c r="A16" s="5">
         <v>10002</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B16" s="5">
         <v>1</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C16" s="5">
         <v>0</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>62</v>
+      <c r="D16" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -1850,161 +2102,163 @@
   <dimension ref="A11:C24"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="2"/>
   <cols>
-    <col min="2" max="2" width="27" customWidth="1"/>
-    <col min="3" max="3" width="28.6666666666667" customWidth="1"/>
+    <col min="1" max="1" width="8.88888888888889" style="1"/>
+    <col min="2" max="2" width="27" style="1" customWidth="1"/>
+    <col min="3" max="3" width="28.6666666666667" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.88888888888889" style="1"/>
   </cols>
   <sheetData>
-    <row r="11" ht="16.35" spans="1:3">
-      <c r="A11" s="1" t="s">
+    <row r="11" ht="15.6" spans="1:3">
+      <c r="A11" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" ht="15.6" spans="1:3">
+      <c r="A12" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" ht="15.6" spans="1:3">
+      <c r="A13" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="12" ht="16.35" spans="1:3">
-      <c r="A12" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="13" ht="16.35" spans="1:3">
-      <c r="A13" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="14" ht="16.35" spans="1:3">
-      <c r="A14" s="1" t="s">
+      <c r="B13" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="14" ht="15.6" spans="1:3">
+      <c r="A14" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="15" ht="16.35" spans="1:3">
-      <c r="A15" s="1">
+      <c r="B14" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="15" ht="15.6" spans="1:3">
+      <c r="A15" s="2">
         <v>10001</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C15" s="1">
+      <c r="B15" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C15" s="2">
         <v>1e-5</v>
       </c>
     </row>
-    <row r="16" ht="16.35" spans="1:3">
-      <c r="A16" s="1">
+    <row r="16" ht="15.6" spans="1:3">
+      <c r="A16" s="2">
         <v>10002</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="3">
         <v>0.1</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C16" s="2">
         <v>1e-5</v>
       </c>
     </row>
-    <row r="17" ht="16.35" spans="1:3">
-      <c r="A17" s="1">
+    <row r="17" ht="15.6" spans="1:3">
+      <c r="A17" s="2">
         <v>10003</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="3">
         <v>0.1</v>
       </c>
-      <c r="C17" s="1">
+      <c r="C17" s="2">
         <v>1e-5</v>
       </c>
     </row>
-    <row r="18" ht="16.35" spans="1:3">
-      <c r="A18" s="1">
+    <row r="18" ht="15.6" spans="1:3">
+      <c r="A18" s="2">
         <v>10004</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18" s="3">
         <v>0.1</v>
       </c>
-      <c r="C18" s="1">
+      <c r="C18" s="2">
         <v>1e-5</v>
       </c>
     </row>
-    <row r="19" ht="16.35" spans="1:3">
-      <c r="A19" s="1">
+    <row r="19" ht="15.6" spans="1:3">
+      <c r="A19" s="2">
         <v>10005</v>
       </c>
-      <c r="B19" s="1">
+      <c r="B19" s="2">
         <v>0.1</v>
       </c>
-      <c r="C19" s="1">
+      <c r="C19" s="2">
         <v>1e-5</v>
       </c>
     </row>
-    <row r="20" ht="16.35" spans="1:3">
-      <c r="A20" s="1">
+    <row r="20" ht="15.6" spans="1:3">
+      <c r="A20" s="2">
         <v>10006</v>
       </c>
-      <c r="B20" s="1">
+      <c r="B20" s="2">
         <v>0.1</v>
       </c>
-      <c r="C20" s="1">
+      <c r="C20" s="2">
         <v>1e-5</v>
       </c>
     </row>
-    <row r="21" ht="16.35" spans="1:3">
-      <c r="A21" s="1">
+    <row r="21" ht="15.6" spans="1:3">
+      <c r="A21" s="2">
         <v>10007</v>
       </c>
-      <c r="B21" s="1">
+      <c r="B21" s="2">
         <v>0.1</v>
       </c>
-      <c r="C21" s="1">
+      <c r="C21" s="2">
         <v>1e-5</v>
       </c>
     </row>
-    <row r="22" ht="16.35" spans="1:3">
-      <c r="A22" s="1">
+    <row r="22" ht="15.6" spans="1:3">
+      <c r="A22" s="2">
         <v>10008</v>
       </c>
-      <c r="B22" s="1">
+      <c r="B22" s="2">
         <v>0.1</v>
       </c>
-      <c r="C22" s="1">
+      <c r="C22" s="2">
         <v>1e-5</v>
       </c>
     </row>
-    <row r="23" ht="16.35" spans="1:3">
-      <c r="A23" s="1">
+    <row r="23" ht="15.6" spans="1:3">
+      <c r="A23" s="2">
         <v>10009</v>
       </c>
-      <c r="B23" s="1">
+      <c r="B23" s="2">
         <v>0.1</v>
       </c>
-      <c r="C23" s="1">
+      <c r="C23" s="2">
         <v>1e-5</v>
       </c>
     </row>
-    <row r="24" ht="16.35" spans="1:3">
-      <c r="A24" s="1">
+    <row r="24" ht="15.6" spans="1:3">
+      <c r="A24" s="2">
         <v>10010</v>
       </c>
-      <c r="B24" s="1">
+      <c r="B24" s="2">
         <v>0.1</v>
       </c>
-      <c r="C24" s="1">
+      <c r="C24" s="2">
         <v>1e-5</v>
       </c>
     </row>

--- a/csharp/Wjybxx.BigCatEditor.Tests/res/test.xlsx
+++ b/csharp/Wjybxx.BigCatEditor.Tests/res/test.xlsx
@@ -4,14 +4,16 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" activeTab="3"/>
+    <workbookView windowWidth="23040" windowHeight="9180" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Skill" sheetId="1" r:id="rId1"/>
     <sheet name="SkillParam" sheetId="2" r:id="rId2"/>
-    <sheet name="Scene" sheetId="3" r:id="rId3"/>
-    <sheet name="Item" sheetId="4" r:id="rId4"/>
-    <sheet name="Test" sheetId="5" r:id="rId5"/>
+    <sheet name="SkillParam.1" sheetId="7" r:id="rId3"/>
+    <sheet name="Scene" sheetId="3" r:id="rId4"/>
+    <sheet name="Item.Base" sheetId="4" r:id="rId5"/>
+    <sheet name="Item.Equip" sheetId="6" r:id="rId6"/>
+    <sheet name="Test" sheetId="5" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="99">
   <si>
     <t>普通表模板</t>
   </si>
@@ -127,6 +129,21 @@
   </si>
   <si>
     <t>默认暴击值</t>
+  </si>
+  <si>
+    <t>测试参数表合并</t>
+  </si>
+  <si>
+    <t>baseHitRate2</t>
+  </si>
+  <si>
+    <t>默认命中率2</t>
+  </si>
+  <si>
+    <t>baseCritRate2</t>
+  </si>
+  <si>
+    <t>默认暴击值2</t>
   </si>
   <si>
     <t>有常量名的数据不可删</t>
@@ -220,6 +237,9 @@
     <t>试炼武馆</t>
   </si>
   <si>
+    <t>C {isRecord: true}</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10.5"/>
@@ -234,6 +254,9 @@
     <t>List&lt;string&gt;</t>
   </si>
   <si>
+    <t>Map&lt;int32,string&gt;</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10.5"/>
@@ -276,6 +299,18 @@
     <t>jumpList#2</t>
   </si>
   <si>
+    <t>jumpList#3</t>
+  </si>
+  <si>
+    <t>jumpMap</t>
+  </si>
+  <si>
+    <t>jumpMap#1</t>
+  </si>
+  <si>
+    <t>jumpMap#2</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10.5"/>
@@ -329,6 +364,12 @@
     <t>跳表2</t>
   </si>
   <si>
+    <t>跳表3</t>
+  </si>
+  <si>
+    <t>测试字典合并</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10.5"/>
@@ -346,6 +387,16 @@
     <t>linker_102</t>
   </si>
   <si>
+    <t>hello
+world</t>
+  </si>
+  <si>
+    <t>{1 : linker_101 }</t>
+  </si>
+  <si>
+    <t>{2 : linker_102 }</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10.5"/>
@@ -361,6 +412,27 @@
   </si>
   <si>
     <t>linker_202</t>
+  </si>
+  <si>
+    <t>{1 : linker_201 }</t>
+  </si>
+  <si>
+    <t>{2 : linker_202 }</t>
+  </si>
+  <si>
+    <t>测试表格继承</t>
+  </si>
+  <si>
+    <t>equipLv</t>
+  </si>
+  <si>
+    <t>装备lv</t>
+  </si>
+  <si>
+    <t>1号装备</t>
+  </si>
+  <si>
+    <t>2号装备</t>
   </si>
   <si>
     <t>double</t>
@@ -1000,7 +1072,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1013,20 +1085,8 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1438,13 +1498,13 @@
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
-      <c r="E7" s="6"/>
+      <c r="E7" s="2"/>
     </row>
     <row r="8" ht="15.6" spans="1:5">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
-      <c r="D8" s="7"/>
+      <c r="D8" s="2"/>
       <c r="E8" s="2"/>
     </row>
     <row r="9" ht="15.6" spans="1:5">
@@ -1452,7 +1512,7 @@
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
-      <c r="E9" s="8"/>
+      <c r="E9" s="2"/>
     </row>
     <row r="10" ht="15.6" spans="1:5">
       <c r="A10" s="2"/>
@@ -1713,6 +1773,148 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="11.8888888888889" style="1" customWidth="1"/>
+    <col min="2" max="2" width="6.66666666666667" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19.7777777777778" style="1" customWidth="1"/>
+    <col min="4" max="4" width="6.66666666666667" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.8888888888889" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.6" spans="1:5">
+      <c r="A1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+    </row>
+    <row r="2" ht="15.6" spans="1:5">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+    </row>
+    <row r="3" ht="15.6" spans="1:5">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4" ht="15.6" spans="1:5">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5" ht="15.6" spans="1:5">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" ht="15.6" spans="1:5">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" ht="15.6" spans="1:5">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" ht="15.6" spans="1:5">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" ht="15.6" spans="1:5">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" ht="15.6" spans="1:5">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11" ht="15.6" spans="1:5">
+      <c r="A11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" ht="15.6" spans="1:5">
+      <c r="A12" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" ht="15.6" spans="1:5">
+      <c r="A13" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0.15</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:F18"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
@@ -1774,7 +1976,7 @@
     <row r="7" ht="15.6" spans="1:6">
       <c r="A7" s="2"/>
       <c r="B7" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -1825,55 +2027,55 @@
     </row>
     <row r="12" ht="15.6" spans="1:6">
       <c r="A12" s="2" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>4</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F12" s="2"/>
     </row>
     <row r="13" ht="15.6" spans="1:6">
       <c r="A13" s="2" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F13" s="2"/>
     </row>
     <row r="14" ht="15.6" spans="1:6">
       <c r="A14" s="2" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F14" s="2"/>
     </row>
@@ -1882,16 +2084,16 @@
         <v>1001</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D15" s="2">
         <v>1</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F15" s="2"/>
     </row>
@@ -1901,13 +2103,13 @@
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D16" s="2">
         <v>2</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="F16" s="2"/>
     </row>
@@ -1916,16 +2118,16 @@
         <v>8001</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D17" s="2">
         <v>20</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="F17" s="2"/>
     </row>
@@ -1943,151 +2145,211 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A11:G16"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <dimension ref="A11:K16"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="4" width="8.88888888888889" style="4"/>
-    <col min="5" max="5" width="16" style="4" customWidth="1"/>
-    <col min="6" max="6" width="14.4444444444444" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.1111111111111" style="4" customWidth="1"/>
-    <col min="8" max="16384" width="8.88888888888889" style="4"/>
+    <col min="1" max="1" width="7.77777777777778" style="1" customWidth="1"/>
+    <col min="2" max="4" width="9.33333333333333" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.8888888888889" style="1" customWidth="1"/>
+    <col min="6" max="8" width="12.6666666666667" style="1" customWidth="1"/>
+    <col min="9" max="9" width="21.2222222222222" style="1" customWidth="1"/>
+    <col min="10" max="11" width="17" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.88888888888889" style="1"/>
   </cols>
   <sheetData>
-    <row r="11" ht="15.6" spans="1:7">
-      <c r="A11" s="5" t="s">
+    <row r="11" ht="15.6" spans="1:11">
+      <c r="A11" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="G11" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="H11" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="12" ht="15.6" spans="1:7">
-      <c r="A12" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="13" ht="15.6" spans="1:7">
-      <c r="A13" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="D13" s="5" t="s">
+      <c r="I11" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+    </row>
+    <row r="12" ht="15.6" spans="1:11">
+      <c r="A12" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+    </row>
+    <row r="13" ht="15.6" spans="1:11">
+      <c r="A13" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E13" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="14" ht="15.6" spans="1:7">
-      <c r="A14" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="E14" s="5" t="s">
+      <c r="E13" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F13" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="G13" s="2" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="15" ht="15.6" spans="1:7">
-      <c r="A15" s="5">
+      <c r="H13" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" ht="15.6" spans="1:11">
+      <c r="A14" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="15" ht="31.2" spans="1:11">
+      <c r="A15" s="2">
         <v>10001</v>
       </c>
-      <c r="B15" s="5">
+      <c r="B15" s="2">
         <v>1</v>
       </c>
-      <c r="C15" s="5">
+      <c r="C15" s="2">
         <v>1</v>
       </c>
-      <c r="D15" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="16" ht="15.6" spans="1:7">
-      <c r="A16" s="5">
+      <c r="D15" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16" ht="15.6" spans="1:11">
+      <c r="A16" s="2">
         <v>10002</v>
       </c>
-      <c r="B16" s="5">
+      <c r="B16" s="2">
         <v>1</v>
       </c>
-      <c r="C16" s="5">
+      <c r="C16" s="2">
         <v>0</v>
       </c>
-      <c r="D16" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>69</v>
+      <c r="D16" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -2096,7 +2358,258 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:M16"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="11.3333333333333" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.2222222222222" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.8888888888889" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.8888888888889" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" ht="15.6" spans="6:13">
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+    </row>
+    <row r="5" ht="15.6" spans="6:13">
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+    </row>
+    <row r="6" ht="15.6" spans="5:13">
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+    </row>
+    <row r="7" ht="15.6" spans="5:13">
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" ht="15.6" spans="5:13">
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+    </row>
+    <row r="9" ht="15.6" spans="5:13">
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+    </row>
+    <row r="10" ht="15.6" spans="5:13">
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+    </row>
+    <row r="11" ht="15.6" spans="1:13">
+      <c r="A11" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+    </row>
+    <row r="12" ht="15.6" spans="1:13">
+      <c r="A12" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+    </row>
+    <row r="13" ht="15.6" spans="1:13">
+      <c r="A13" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+    </row>
+    <row r="14" ht="15.6" spans="1:13">
+      <c r="A14" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+    </row>
+    <row r="15" ht="15.6" spans="1:10">
+      <c r="A15" s="2">
+        <v>11001</v>
+      </c>
+      <c r="B15" s="2">
+        <v>1</v>
+      </c>
+      <c r="C15" s="2">
+        <v>1</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2">
+        <v>10</v>
+      </c>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+    </row>
+    <row r="16" ht="15.6" spans="1:10">
+      <c r="A16" s="2">
+        <v>11002</v>
+      </c>
+      <c r="B16" s="2">
+        <v>1</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2">
+        <v>20</v>
+      </c>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A11:C24"/>
@@ -2121,35 +2634,35 @@
     </row>
     <row r="12" ht="15.6" spans="1:3">
       <c r="A12" s="2" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13" ht="15.6" spans="1:3">
       <c r="A13" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" ht="15.6" spans="1:3">
       <c r="A14" s="2" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15" ht="15.6" spans="1:3">
@@ -2157,7 +2670,7 @@
         <v>10001</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="C15" s="2">
         <v>1e-5</v>

--- a/csharp/Wjybxx.BigCatEditor.Tests/res/test.xlsx
+++ b/csharp/Wjybxx.BigCatEditor.Tests/res/test.xlsx
@@ -4,11 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" activeTab="2"/>
+    <workbookView windowWidth="23040" windowHeight="9180" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Skill" sheetId="1" r:id="rId1"/>
-    <sheet name="SkillParam" sheetId="2" r:id="rId2"/>
+    <sheet name="SkillParam.0" sheetId="2" r:id="rId2"/>
     <sheet name="SkillParam.1" sheetId="7" r:id="rId3"/>
     <sheet name="Scene" sheetId="3" r:id="rId4"/>
     <sheet name="Item.Base" sheetId="4" r:id="rId5"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="111">
   <si>
     <t>普通表模板</t>
   </si>
@@ -147,6 +147,9 @@
   </si>
   <si>
     <t>有常量名的数据不可删</t>
+  </si>
+  <si>
+    <t>测试自定义结构</t>
   </si>
   <si>
     <r>
@@ -171,6 +174,9 @@
     </r>
   </si>
   <si>
+    <t>DVector3</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
@@ -191,6 +197,9 @@
     </r>
   </si>
   <si>
+    <t>bornPos</t>
+  </si>
+  <si>
     <t>场景id</t>
   </si>
   <si>
@@ -204,6 +213,9 @@
   </si>
   <si>
     <t>场景介绍</t>
+  </si>
+  <si>
+    <t>出生点</t>
   </si>
   <si>
     <r>
@@ -220,7 +232,13 @@
     <t>新手副本</t>
   </si>
   <si>
+    <t>[0, 0, 0]</t>
+  </si>
+  <si>
     <t>新手副本2</t>
+  </si>
+  <si>
+    <t>[50, 0, 50]</t>
   </si>
   <si>
     <r>
@@ -237,6 +255,12 @@
     <t>试炼武馆</t>
   </si>
   <si>
+    <t>{x: 1, y:1, z: 1}</t>
+  </si>
+  <si>
+    <t>测试枚举生成</t>
+  </si>
+  <si>
     <t>C {isRecord: true}</t>
   </si>
   <si>
@@ -290,6 +314,9 @@
     </r>
   </si>
   <si>
+    <t>enumName</t>
+  </si>
+  <si>
     <t>jumpList</t>
   </si>
   <si>
@@ -355,6 +382,9 @@
     </r>
   </si>
   <si>
+    <t>枚举名</t>
+  </si>
+  <si>
     <t>测试List合并</t>
   </si>
   <si>
@@ -381,6 +411,9 @@
     </r>
   </si>
   <si>
+    <t>firstItemId</t>
+  </si>
+  <si>
     <t>linker_101</t>
   </si>
   <si>
@@ -430,6 +463,9 @@
   </si>
   <si>
     <t>1号装备</t>
+  </si>
+  <si>
+    <t>firstEquipId</t>
   </si>
   <si>
     <t>2号装备</t>
@@ -1915,99 +1951,26 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F18"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <dimension ref="A7:F17"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="15.6" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="10.6666666666667" customWidth="1"/>
-    <col min="2" max="2" width="15.5555555555556" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="9.66666666666667" customWidth="1"/>
-    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="1" max="5" width="10.6666666666667" style="2" customWidth="1"/>
+    <col min="6" max="6" width="16.4444444444444" style="2" customWidth="1"/>
+    <col min="7" max="7" width="10.6666666666667" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.6" spans="1:6">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-    </row>
-    <row r="2" ht="15.6" spans="1:6">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-    </row>
-    <row r="3" ht="15.6" spans="1:6">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-    </row>
-    <row r="4" ht="15.6" spans="1:6">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-    </row>
-    <row r="5" ht="15.6" spans="1:6">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-    </row>
-    <row r="6" ht="15.6" spans="1:6">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-    </row>
-    <row r="7" ht="15.6" spans="1:6">
-      <c r="A7" s="2"/>
+    <row r="7" spans="2:6">
       <c r="B7" s="2" t="s">
         <v>37</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-    </row>
-    <row r="8" ht="15.6" spans="1:6">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-    </row>
-    <row r="9" ht="15.6" spans="1:6">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-    </row>
-    <row r="10" ht="15.6" spans="1:6">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-    </row>
-    <row r="11" ht="15.6" spans="1:6">
+      <c r="F7" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" s="2" t="s">
         <v>2</v>
       </c>
@@ -2023,121 +1986,127 @@
       <c r="E11" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F11" s="2"/>
-    </row>
-    <row r="12" ht="15.6" spans="1:6">
+      <c r="F11" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>4</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F12" s="2"/>
-    </row>
-    <row r="13" ht="15.6" spans="1:6">
+        <v>40</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F13" s="2"/>
-    </row>
-    <row r="14" ht="15.6" spans="1:6">
+        <v>45</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F14" s="2"/>
-    </row>
-    <row r="15" ht="15.6" spans="1:6">
+        <v>51</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15" s="2">
         <v>1001</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D15" s="2">
         <v>1</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F15" s="2"/>
-    </row>
-    <row r="16" ht="15.6" spans="1:6">
+        <v>54</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16" s="2">
         <v>1002</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D16" s="2">
         <v>2</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F16" s="2"/>
-    </row>
-    <row r="17" ht="15.6" spans="1:6">
+        <v>56</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" s="2">
         <v>8001</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D17" s="2">
         <v>20</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F17" s="2"/>
-    </row>
-    <row r="18" ht="15.6" spans="1:6">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
+        <v>59</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>60</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2148,19 +2117,25 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A11:K16"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="7.77777777777778" style="1" customWidth="1"/>
     <col min="2" max="4" width="9.33333333333333" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.8888888888889" style="1" customWidth="1"/>
-    <col min="6" max="8" width="12.6666666666667" style="1" customWidth="1"/>
-    <col min="9" max="9" width="21.2222222222222" style="1" customWidth="1"/>
-    <col min="10" max="11" width="17" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.88888888888889" style="1"/>
+    <col min="5" max="5" width="13.2222222222222" style="1" customWidth="1"/>
+    <col min="6" max="6" width="19" style="1" customWidth="1"/>
+    <col min="7" max="9" width="12.6666666666667" style="1" customWidth="1"/>
+    <col min="10" max="10" width="21.2222222222222" style="1" customWidth="1"/>
+    <col min="11" max="12" width="17" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.88888888888889" style="1"/>
   </cols>
   <sheetData>
-    <row r="11" ht="15.6" spans="1:11">
+    <row r="1" spans="5:5">
+      <c r="E1" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" ht="15.6" spans="1:12">
       <c r="A11" s="2" t="s">
         <v>2</v>
       </c>
@@ -2174,10 +2149,10 @@
         <v>3</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>54</v>
+        <v>3</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>3</v>
@@ -2188,111 +2163,123 @@
       <c r="I11" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="J11" s="2"/>
+      <c r="J11" s="2" t="s">
+        <v>3</v>
+      </c>
       <c r="K11" s="2"/>
-    </row>
-    <row r="12" ht="15.6" spans="1:11">
+      <c r="L11" s="2"/>
+    </row>
+    <row r="12" ht="15.6" spans="1:12">
       <c r="A12" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="J12" s="2"/>
+        <v>40</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>65</v>
+      </c>
       <c r="K12" s="2"/>
-    </row>
-    <row r="13" ht="15.6" spans="1:11">
+      <c r="L12" s="2"/>
+    </row>
+    <row r="13" ht="15.6" spans="1:12">
       <c r="A13" s="2" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="14" ht="15.6" spans="1:11">
+        <v>75</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="14" ht="15.6" spans="1:12">
       <c r="A14" s="2" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="15" ht="31.2" spans="1:11">
+        <v>83</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="15" ht="31.2" spans="1:12">
       <c r="A15" s="2">
         <v>10001</v>
       </c>
@@ -2303,27 +2290,30 @@
         <v>1</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2" t="s">
-        <v>78</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F15" s="2"/>
       <c r="G15" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2" t="s">
-        <v>81</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="J15" s="2"/>
       <c r="K15" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="16" ht="15.6" spans="1:11">
+        <v>92</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="16" ht="15.6" spans="1:12">
       <c r="A16" s="2">
         <v>10002</v>
       </c>
@@ -2334,22 +2324,23 @@
         <v>0</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="E16" s="2"/>
-      <c r="F16" s="2" t="s">
-        <v>84</v>
-      </c>
+      <c r="F16" s="2"/>
       <c r="G16" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="H16" s="2"/>
+        <v>95</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>96</v>
+      </c>
       <c r="I16" s="2"/>
-      <c r="J16" s="2" t="s">
-        <v>86</v>
-      </c>
+      <c r="J16" s="2"/>
       <c r="K16" s="2" t="s">
-        <v>87</v>
+        <v>97</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -2361,23 +2352,22 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="11.3333333333333" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.2222222222222" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.8888888888889" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.8888888888889" style="1" customWidth="1"/>
+    <col min="1" max="1" width="14.1111111111111" style="1" customWidth="1"/>
+    <col min="2" max="4" width="9.33333333333333" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.2222222222222" style="1" customWidth="1"/>
+    <col min="6" max="6" width="19" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9.22222222222222" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="4" ht="15.6" spans="6:13">
-      <c r="F4" s="2"/>
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" ht="15.6" spans="7:14">
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
@@ -2385,9 +2375,9 @@
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
-    </row>
-    <row r="5" ht="15.6" spans="6:13">
-      <c r="F5" s="2"/>
+      <c r="N4" s="2"/>
+    </row>
+    <row r="5" ht="15.6" spans="7:14">
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
@@ -2395,9 +2385,9 @@
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
-    </row>
-    <row r="6" ht="15.6" spans="5:13">
-      <c r="E6" s="2"/>
+      <c r="N5" s="2"/>
+    </row>
+    <row r="6" ht="15.6" spans="6:14">
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
@@ -2406,9 +2396,9 @@
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
-    </row>
-    <row r="7" ht="15.6" spans="5:13">
-      <c r="E7" s="2"/>
+      <c r="N6" s="2"/>
+    </row>
+    <row r="7" ht="15.6" spans="6:14">
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
@@ -2417,9 +2407,9 @@
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
-    </row>
-    <row r="8" ht="15.6" spans="5:13">
-      <c r="E8" s="2"/>
+      <c r="N7" s="2"/>
+    </row>
+    <row r="8" ht="15.6" spans="6:14">
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
@@ -2428,9 +2418,9 @@
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
-    </row>
-    <row r="9" ht="15.6" spans="5:13">
-      <c r="E9" s="2"/>
+      <c r="N8" s="2"/>
+    </row>
+    <row r="9" ht="15.6" spans="6:14">
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
@@ -2439,9 +2429,9 @@
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
-    </row>
-    <row r="10" ht="15.6" spans="5:13">
-      <c r="E10" s="2"/>
+      <c r="N9" s="2"/>
+    </row>
+    <row r="10" ht="15.6" spans="6:14">
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
@@ -2450,8 +2440,9 @@
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
-    </row>
-    <row r="11" ht="15.6" spans="1:13">
+      <c r="N10" s="2"/>
+    </row>
+    <row r="11" ht="15.6" spans="1:14">
       <c r="A11" s="2" t="s">
         <v>2</v>
       </c>
@@ -2465,101 +2456,113 @@
         <v>3</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>54</v>
+        <v>3</v>
       </c>
       <c r="F11" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
-    </row>
-    <row r="12" ht="15.6" spans="1:13">
+      <c r="N11" s="2"/>
+    </row>
+    <row r="12" ht="15.6" spans="1:14">
       <c r="A12" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="F12" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
-    </row>
-    <row r="13" ht="15.6" spans="1:13">
+      <c r="N12" s="2"/>
+    </row>
+    <row r="13" ht="15.6" spans="1:14">
       <c r="A13" s="2" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G13" s="2"/>
+        <v>70</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>100</v>
+      </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
-    </row>
-    <row r="14" ht="15.6" spans="1:13">
+      <c r="N13" s="2"/>
+    </row>
+    <row r="14" ht="15.6" spans="1:14">
       <c r="A14" s="2" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G14" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>101</v>
+      </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
-    </row>
-    <row r="15" ht="15.6" spans="1:10">
+      <c r="N14" s="2"/>
+    </row>
+    <row r="15" ht="15.6" spans="1:11">
       <c r="A15" s="2">
         <v>11001</v>
       </c>
@@ -2570,18 +2573,21 @@
         <v>1</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2">
+        <v>102</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2">
         <v>10</v>
       </c>
-      <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
-    </row>
-    <row r="16" ht="15.6" spans="1:10">
+      <c r="K15" s="2"/>
+    </row>
+    <row r="16" ht="15.6" spans="1:11">
       <c r="A16" s="2">
         <v>11002</v>
       </c>
@@ -2592,16 +2598,17 @@
         <v>0</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E16" s="2"/>
-      <c r="F16" s="2">
+      <c r="F16" s="2"/>
+      <c r="G16" s="2">
         <v>20</v>
       </c>
-      <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2634,35 +2641,35 @@
     </row>
     <row r="12" ht="15.6" spans="1:3">
       <c r="A12" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13" ht="15.6" spans="1:3">
       <c r="A13" s="2" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
     </row>
     <row r="14" ht="15.6" spans="1:3">
       <c r="A14" s="2" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15" ht="15.6" spans="1:3">
@@ -2670,7 +2677,7 @@
         <v>10001</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="C15" s="2">
         <v>1e-5</v>

--- a/csharp/Wjybxx.BigCatEditor.Tests/res/test.xlsx
+++ b/csharp/Wjybxx.BigCatEditor.Tests/res/test.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" activeTab="3"/>
+    <workbookView windowWidth="23040" windowHeight="9180" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Skill" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="113">
   <si>
     <t>普通表模板</t>
   </si>
@@ -101,6 +101,9 @@
     <t>参数表模板</t>
   </si>
   <si>
+    <t>测试下常量生成</t>
+  </si>
+  <si>
     <t>options</t>
   </si>
   <si>
@@ -114,6 +117,9 @@
   </si>
   <si>
     <t>comment</t>
+  </si>
+  <si>
+    <t>C/S {isConst: true}</t>
   </si>
   <si>
     <t>float</t>
@@ -1668,7 +1674,7 @@
   <dimension ref="A1:E13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="11.8888888888889" style="1" customWidth="1"/>
+    <col min="1" max="1" width="19.7777777777778" style="1" customWidth="1"/>
     <col min="2" max="2" width="6.66666666666667" style="1" customWidth="1"/>
     <col min="3" max="3" width="19.7777777777778" style="1" customWidth="1"/>
     <col min="4" max="4" width="6.66666666666667" style="1" customWidth="1"/>
@@ -1686,7 +1692,9 @@
       <c r="E1" s="2"/>
     </row>
     <row r="2" ht="15.6" spans="1:5">
-      <c r="A2" s="2"/>
+      <c r="A2" s="2" t="s">
+        <v>22</v>
+      </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -1750,53 +1758,53 @@
     </row>
     <row r="11" ht="15.6" spans="1:5">
       <c r="A11" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" ht="15.6" spans="1:5">
       <c r="A12" s="2" t="s">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D12" s="2">
         <v>0.8</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" ht="15.6" spans="1:5">
       <c r="A13" s="2" t="s">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D13" s="2">
         <v>0.15</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1821,7 +1829,7 @@
   <sheetData>
     <row r="1" ht="15.6" spans="1:5">
       <c r="A1" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1893,19 +1901,19 @@
     </row>
     <row r="11" ht="15.6" spans="1:5">
       <c r="A11" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" ht="15.6" spans="1:5">
@@ -1913,16 +1921,16 @@
         <v>2</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D12" s="2">
         <v>0.8</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" ht="15.6" spans="1:5">
@@ -1930,16 +1938,16 @@
         <v>2</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D13" s="2">
         <v>0.15</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1961,13 +1969,10 @@
   <sheetData>
     <row r="7" spans="2:6">
       <c r="B7" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
+        <v>39</v>
+      </c>
       <c r="F7" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1992,62 +1997,62 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>4</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2055,37 +2060,36 @@
         <v>1001</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D15" s="2">
         <v>1</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2">
         <v>1002</v>
       </c>
-      <c r="B16" s="2"/>
       <c r="C16" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D16" s="2">
         <v>2</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -2093,19 +2097,19 @@
         <v>8001</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D17" s="2">
         <v>20</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -2132,7 +2136,7 @@
   <sheetData>
     <row r="1" spans="5:5">
       <c r="E1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" ht="15.6" spans="1:12">
@@ -2152,7 +2156,7 @@
         <v>3</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>3</v>
@@ -2171,112 +2175,112 @@
     </row>
     <row r="12" ht="15.6" spans="1:12">
       <c r="A12" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
     </row>
     <row r="13" ht="15.6" spans="1:12">
       <c r="A13" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" ht="15.6" spans="1:12">
       <c r="A14" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I14" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="K14" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="J14" s="2" t="s">
+      <c r="L14" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="15" ht="31.2" spans="1:12">
@@ -2290,27 +2294,27 @@
         <v>1</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J15" s="2"/>
       <c r="K15" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" ht="15.6" spans="1:12">
@@ -2324,23 +2328,23 @@
         <v>0</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -2364,7 +2368,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" ht="15.6" spans="7:14">
@@ -2459,7 +2463,7 @@
         <v>3</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>2</v>
@@ -2474,22 +2478,22 @@
     </row>
     <row r="12" ht="15.6" spans="1:14">
       <c r="A12" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>4</v>
@@ -2504,25 +2508,25 @@
     </row>
     <row r="13" ht="15.6" spans="1:14">
       <c r="A13" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
@@ -2534,25 +2538,25 @@
     </row>
     <row r="14" ht="15.6" spans="1:14">
       <c r="A14" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
@@ -2573,10 +2577,10 @@
         <v>1</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2">
@@ -2598,7 +2602,7 @@
         <v>0</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
@@ -2641,35 +2645,35 @@
     </row>
     <row r="12" ht="15.6" spans="1:3">
       <c r="A12" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13" ht="15.6" spans="1:3">
       <c r="A13" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" ht="15.6" spans="1:3">
       <c r="A14" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15" ht="15.6" spans="1:3">
@@ -2677,7 +2681,7 @@
         <v>10001</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C15" s="2">
         <v>1e-5</v>

--- a/csharp/Wjybxx.BigCatEditor.Tests/res/test.xlsx
+++ b/csharp/Wjybxx.BigCatEditor.Tests/res/test.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" activeTab="1"/>
+    <workbookView windowWidth="23040" windowHeight="9180" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Skill" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="134">
   <si>
     <t>普通表模板</t>
   </si>
@@ -267,6 +267,9 @@
     <t>测试枚举生成</t>
   </si>
   <si>
+    <t>Element列可以不配置类型</t>
+  </si>
+  <si>
     <t>C {isRecord: true}</t>
   </si>
   <si>
@@ -477,6 +480,18 @@
     <t>2号装备</t>
   </si>
   <si>
+    <t>值相等的字符串会指向同一个对象</t>
+  </si>
+  <si>
+    <t>测试分散配置</t>
+  </si>
+  <si>
+    <t>字符串配置在一起的时候，特殊字符串要加引号</t>
+  </si>
+  <si>
+    <t>C/S {intern: true}</t>
+  </si>
+  <si>
     <t>double</t>
   </si>
   <si>
@@ -486,13 +501,61 @@
     <t>rate2</t>
   </si>
   <si>
+    <t>list1</t>
+  </si>
+  <si>
+    <t>list2</t>
+  </si>
+  <si>
+    <t>list2#1</t>
+  </si>
+  <si>
+    <t>list2#2</t>
+  </si>
+  <si>
     <t>概率</t>
   </si>
   <si>
     <t>概率-会被导出为科学计数法</t>
   </si>
   <si>
+    <t>测试字符串池化</t>
+  </si>
+  <si>
     <t>123.45678901234567890</t>
+  </si>
+  <si>
+    <t>[abc, "123"]</t>
+  </si>
+  <si>
+    <t>大A今天3400点，明天怎么走？</t>
+  </si>
+  <si>
+    <t>大A今天3401点，明天怎么走？</t>
+  </si>
+  <si>
+    <t>大A今天3402点，明天怎么走？</t>
+  </si>
+  <si>
+    <t>大A今天3403点，明天怎么走？</t>
+  </si>
+  <si>
+    <t>大A今天3404点，明天怎么走？</t>
+  </si>
+  <si>
+    <t>大A今天3405点，明天怎么走？</t>
+  </si>
+  <si>
+    <t>大A今天3406点，明天怎么走？</t>
+  </si>
+  <si>
+    <t>大A今天3407点，明天怎么走？</t>
+  </si>
+  <si>
+    <t>大A今天3408点，明天怎么走？</t>
+  </si>
+  <si>
+    <t>大A今天3409点，明天怎么走？</t>
   </si>
 </sst>
 </file>
@@ -2134,9 +2197,15 @@
     <col min="13" max="16384" width="8.88888888888889" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="5:5">
+    <row r="1" spans="5:10">
       <c r="E1" s="1" t="s">
         <v>63</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="11" ht="15.6" spans="1:12">
@@ -2156,7 +2225,7 @@
         <v>3</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>3</v>
@@ -2181,7 +2250,7 @@
         <v>41</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>42</v>
@@ -2190,7 +2259,7 @@
         <v>42</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>42</v>
@@ -2202,85 +2271,85 @@
         <v>42</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
     </row>
     <row r="13" ht="15.6" spans="1:12">
       <c r="A13" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" ht="15.6" spans="1:12">
       <c r="A14" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H14" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="K14" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="I14" s="2" t="s">
+      <c r="L14" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="15" ht="31.2" spans="1:12">
@@ -2294,27 +2363,27 @@
         <v>1</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J15" s="2"/>
       <c r="K15" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" ht="15.6" spans="1:12">
@@ -2328,23 +2397,23 @@
         <v>0</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -2356,22 +2425,22 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="14.1111111111111" style="1" customWidth="1"/>
     <col min="2" max="4" width="9.33333333333333" style="1" customWidth="1"/>
     <col min="5" max="5" width="13.2222222222222" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19" style="1" customWidth="1"/>
-    <col min="7" max="7" width="9.22222222222222" customWidth="1"/>
+    <col min="6" max="6" width="9.22222222222222" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="4" ht="15.6" spans="7:14">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" ht="15.6" spans="6:13">
+      <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
@@ -2379,9 +2448,9 @@
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-    </row>
-    <row r="5" ht="15.6" spans="7:14">
+    </row>
+    <row r="5" ht="15.6" spans="6:13">
+      <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
@@ -2389,9 +2458,8 @@
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
-    </row>
-    <row r="6" ht="15.6" spans="6:14">
+    </row>
+    <row r="6" ht="15.6" spans="6:13">
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
@@ -2400,9 +2468,8 @@
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
-    </row>
-    <row r="7" ht="15.6" spans="6:14">
+    </row>
+    <row r="7" ht="15.6" spans="6:13">
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
@@ -2411,9 +2478,8 @@
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
-    </row>
-    <row r="8" ht="15.6" spans="6:14">
+    </row>
+    <row r="8" ht="15.6" spans="6:13">
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
@@ -2422,9 +2488,8 @@
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
-    </row>
-    <row r="9" ht="15.6" spans="6:14">
+    </row>
+    <row r="9" ht="15.6" spans="6:13">
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
@@ -2433,9 +2498,8 @@
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
-    </row>
-    <row r="10" ht="15.6" spans="6:14">
+    </row>
+    <row r="10" ht="15.6" spans="6:13">
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
@@ -2444,9 +2508,8 @@
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
-    </row>
-    <row r="11" ht="15.6" spans="1:14">
+    </row>
+    <row r="11" ht="15.6" spans="1:13">
       <c r="A11" s="2" t="s">
         <v>2</v>
       </c>
@@ -2463,20 +2526,17 @@
         <v>3</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="G11" s="2" t="s">
         <v>2</v>
       </c>
+      <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
-    </row>
-    <row r="12" ht="15.6" spans="1:14">
+    </row>
+    <row r="12" ht="15.6" spans="1:13">
       <c r="A12" s="2" t="s">
         <v>41</v>
       </c>
@@ -2484,7 +2544,7 @@
         <v>41</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>42</v>
@@ -2493,80 +2553,71 @@
         <v>42</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G12" s="2" t="s">
         <v>4</v>
       </c>
+      <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
-    </row>
-    <row r="13" ht="15.6" spans="1:14">
+    </row>
+    <row r="13" ht="15.6" spans="1:13">
       <c r="A13" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>102</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
-    </row>
-    <row r="14" ht="15.6" spans="1:14">
+    </row>
+    <row r="14" ht="15.6" spans="1:13">
       <c r="A14" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>103</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
-      <c r="N14" s="2"/>
-    </row>
-    <row r="15" ht="15.6" spans="1:11">
+    </row>
+    <row r="15" ht="15.6" spans="1:10">
       <c r="A15" s="2">
         <v>11001</v>
       </c>
@@ -2577,21 +2628,20 @@
         <v>1</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2">
+        <v>106</v>
+      </c>
+      <c r="F15" s="2">
         <v>10</v>
       </c>
+      <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-    </row>
-    <row r="16" ht="15.6" spans="1:11">
+    </row>
+    <row r="16" ht="15.6" spans="1:10">
       <c r="A16" s="2">
         <v>11002</v>
       </c>
@@ -2602,17 +2652,16 @@
         <v>0</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2">
+      <c r="F16" s="2">
         <v>20</v>
       </c>
+      <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2623,16 +2672,32 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A11:C24"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="2"/>
+  <dimension ref="A4:G24"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="8.88888888888889" style="1"/>
     <col min="2" max="2" width="27" style="1" customWidth="1"/>
     <col min="3" max="3" width="28.6666666666667" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.88888888888889" style="1"/>
+    <col min="4" max="4" width="34.4444444444444" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.4444444444444" style="1" customWidth="1"/>
+    <col min="6" max="7" width="29" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.88888888888889" style="1"/>
   </cols>
   <sheetData>
-    <row r="11" ht="15.6" spans="1:3">
+    <row r="4" spans="4:5">
+      <c r="D4" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="5" spans="4:4">
+      <c r="D5" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="11" ht="15.6" spans="1:7">
       <c r="A11" s="2" t="s">
         <v>2</v>
       </c>
@@ -2642,52 +2707,101 @@
       <c r="C11" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" ht="15.6" spans="1:3">
+      <c r="D11" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+    </row>
+    <row r="12" ht="15.6" spans="1:7">
       <c r="A12" s="2" t="s">
         <v>41</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="13" ht="15.6" spans="1:3">
+        <v>112</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+    </row>
+    <row r="13" ht="15.6" spans="1:7">
       <c r="A13" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="14" ht="15.6" spans="1:3">
+        <v>114</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="14" ht="15.6" spans="1:7">
       <c r="A14" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="15" ht="15.6" spans="1:3">
+        <v>120</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="15" ht="15.6" spans="1:7">
       <c r="A15" s="2">
         <v>10001</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="C15" s="2">
         <v>1e-5</v>
       </c>
-    </row>
-    <row r="16" ht="15.6" spans="1:3">
+      <c r="D15" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="16" ht="15.6" spans="1:7">
       <c r="A16" s="2">
         <v>10002</v>
       </c>
@@ -2697,8 +2811,17 @@
       <c r="C16" s="2">
         <v>1e-5</v>
       </c>
-    </row>
-    <row r="17" ht="15.6" spans="1:3">
+      <c r="D16" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="17" ht="15.6" spans="1:7">
       <c r="A17" s="2">
         <v>10003</v>
       </c>
@@ -2708,8 +2831,17 @@
       <c r="C17" s="2">
         <v>1e-5</v>
       </c>
-    </row>
-    <row r="18" ht="15.6" spans="1:3">
+      <c r="D17" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="18" ht="15.6" spans="1:7">
       <c r="A18" s="2">
         <v>10004</v>
       </c>
@@ -2719,8 +2851,17 @@
       <c r="C18" s="2">
         <v>1e-5</v>
       </c>
-    </row>
-    <row r="19" ht="15.6" spans="1:3">
+      <c r="D18" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="19" ht="15.6" spans="1:7">
       <c r="A19" s="2">
         <v>10005</v>
       </c>
@@ -2730,8 +2871,17 @@
       <c r="C19" s="2">
         <v>1e-5</v>
       </c>
-    </row>
-    <row r="20" ht="15.6" spans="1:3">
+      <c r="D19" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="20" ht="15.6" spans="1:7">
       <c r="A20" s="2">
         <v>10006</v>
       </c>
@@ -2741,8 +2891,17 @@
       <c r="C20" s="2">
         <v>1e-5</v>
       </c>
-    </row>
-    <row r="21" ht="15.6" spans="1:3">
+      <c r="D20" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="21" ht="15.6" spans="1:7">
       <c r="A21" s="2">
         <v>10007</v>
       </c>
@@ -2752,8 +2911,17 @@
       <c r="C21" s="2">
         <v>1e-5</v>
       </c>
-    </row>
-    <row r="22" ht="15.6" spans="1:3">
+      <c r="D21" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="22" ht="15.6" spans="1:7">
       <c r="A22" s="2">
         <v>10008</v>
       </c>
@@ -2763,8 +2931,17 @@
       <c r="C22" s="2">
         <v>1e-5</v>
       </c>
-    </row>
-    <row r="23" ht="15.6" spans="1:3">
+      <c r="D22" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="23" ht="15.6" spans="1:7">
       <c r="A23" s="2">
         <v>10009</v>
       </c>
@@ -2774,8 +2951,17 @@
       <c r="C23" s="2">
         <v>1e-5</v>
       </c>
-    </row>
-    <row r="24" ht="15.6" spans="1:3">
+      <c r="D23" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="24" ht="15.6" spans="1:7">
       <c r="A24" s="2">
         <v>10010</v>
       </c>
@@ -2784,6 +2970,15 @@
       </c>
       <c r="C24" s="2">
         <v>1e-5</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>133</v>
       </c>
     </row>
   </sheetData>

--- a/csharp/Wjybxx.BigCatEditor.Tests/res/test.xlsx
+++ b/csharp/Wjybxx.BigCatEditor.Tests/res/test.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" activeTab="6"/>
+    <workbookView windowWidth="23040" windowHeight="9180" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Skill" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="137">
   <si>
     <t>普通表模板</t>
   </si>
@@ -468,13 +468,22 @@
     <t>equipLv</t>
   </si>
   <si>
+    <t>flags</t>
+  </si>
+  <si>
     <t>装备lv</t>
   </si>
   <si>
+    <t>测试Flags</t>
+  </si>
+  <si>
     <t>1号装备</t>
   </si>
   <si>
     <t>firstEquipId</t>
+  </si>
+  <si>
+    <t>1 | 32 | 64</t>
   </si>
   <si>
     <t>2号装备</t>
@@ -2221,9 +2230,7 @@
       <c r="D11" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>3</v>
-      </c>
+      <c r="E11" s="2"/>
       <c r="F11" s="2" t="s">
         <v>65</v>
       </c>
@@ -2432,6 +2439,7 @@
     <col min="2" max="4" width="9.33333333333333" style="1" customWidth="1"/>
     <col min="5" max="5" width="13.2222222222222" style="1" customWidth="1"/>
     <col min="6" max="6" width="9.22222222222222" customWidth="1"/>
+    <col min="7" max="7" width="11.2222222222222" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
@@ -2522,13 +2530,13 @@
       <c r="D11" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>3</v>
-      </c>
+      <c r="E11" s="2"/>
       <c r="F11" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G11" s="2"/>
+      <c r="G11" s="2" t="s">
+        <v>2</v>
+      </c>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
@@ -2555,7 +2563,9 @@
       <c r="F12" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G12" s="2"/>
+      <c r="G12" s="2" t="s">
+        <v>4</v>
+      </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
@@ -2582,7 +2592,9 @@
       <c r="F13" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="G13" s="2"/>
+      <c r="G13" s="2" t="s">
+        <v>104</v>
+      </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
@@ -2607,9 +2619,11 @@
         <v>84</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="G14" s="2"/>
+        <v>105</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>106</v>
+      </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
@@ -2628,15 +2642,17 @@
         <v>1</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F15" s="2">
         <v>10</v>
       </c>
-      <c r="G15" s="2"/>
+      <c r="G15" s="2" t="s">
+        <v>109</v>
+      </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
@@ -2652,13 +2668,15 @@
         <v>0</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2">
         <v>20</v>
       </c>
-      <c r="G16" s="2"/>
+      <c r="G16" s="2" t="s">
+        <v>109</v>
+      </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
@@ -2686,15 +2704,15 @@
   <sheetData>
     <row r="4" spans="4:5">
       <c r="D4" s="1" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" s="1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" ht="15.6" spans="1:7">
@@ -2708,10 +2726,10 @@
         <v>2</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
@@ -2721,10 +2739,10 @@
         <v>41</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>67</v>
@@ -2740,22 +2758,22 @@
         <v>69</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" ht="15.6" spans="1:7">
@@ -2763,22 +2781,22 @@
         <v>80</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="15" ht="15.6" spans="1:7">
@@ -2786,19 +2804,19 @@
         <v>10001</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C15" s="2">
         <v>1e-5</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="16" ht="15.6" spans="1:7">
@@ -2812,13 +2830,13 @@
         <v>1e-5</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="17" ht="15.6" spans="1:7">
@@ -2832,13 +2850,13 @@
         <v>1e-5</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="18" ht="15.6" spans="1:7">
@@ -2852,13 +2870,13 @@
         <v>1e-5</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="19" ht="15.6" spans="1:7">
@@ -2872,13 +2890,13 @@
         <v>1e-5</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="20" ht="15.6" spans="1:7">
@@ -2892,13 +2910,13 @@
         <v>1e-5</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="21" ht="15.6" spans="1:7">
@@ -2912,13 +2930,13 @@
         <v>1e-5</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="22" ht="15.6" spans="1:7">
@@ -2932,13 +2950,13 @@
         <v>1e-5</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="23" ht="15.6" spans="1:7">
@@ -2952,13 +2970,13 @@
         <v>1e-5</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="24" ht="15.6" spans="1:7">
@@ -2972,13 +2990,13 @@
         <v>1e-5</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
